--- a/resources/templates/standard/L1200-07.xlsx
+++ b/resources/templates/standard/L1200-07.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>구 분</t>
   </si>
@@ -576,7 +579,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -609,55 +614,55 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="4"/>
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F7" s="4"/>
     </row>
     <row r="8" ht="39.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -675,7 +680,7 @@
     </row>
     <row r="10" ht="39.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -693,7 +698,7 @@
     </row>
     <row r="12" ht="39.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -711,7 +716,7 @@
     </row>
     <row r="14" ht="39.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
